--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/37.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/37.xlsx
@@ -426,13 +426,13 @@
         <v>-7.714419866570363</v>
       </c>
       <c r="E2">
-        <v>-10.64004573496777</v>
+        <v>-7.554053723804702</v>
       </c>
       <c r="F2">
-        <v>-1.763641564749615</v>
+        <v>-1.059908664640517</v>
       </c>
       <c r="G2">
-        <v>-8.712380408593511</v>
+        <v>-6.948041326307612</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.000762429780561</v>
       </c>
       <c r="E3">
-        <v>-11.92350583822171</v>
+        <v>-8.372013869914168</v>
       </c>
       <c r="F3">
-        <v>-1.6986876199613</v>
+        <v>-0.9998321471198859</v>
       </c>
       <c r="G3">
-        <v>-8.540211432147888</v>
+        <v>-6.810236583254053</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.383432531419082</v>
       </c>
       <c r="E4">
-        <v>-12.20968728161044</v>
+        <v>-8.695197474419578</v>
       </c>
       <c r="F4">
-        <v>-1.458089964552989</v>
+        <v>-0.3837985039451719</v>
       </c>
       <c r="G4">
-        <v>-8.511579492820173</v>
+        <v>-6.568348211113348</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.776506801060702</v>
       </c>
       <c r="E5">
-        <v>-12.50859373696073</v>
+        <v>-9.796445369026879</v>
       </c>
       <c r="F5">
-        <v>-1.561362528660003</v>
+        <v>-0.4716667478297267</v>
       </c>
       <c r="G5">
-        <v>-8.655789180357768</v>
+        <v>-5.890956426273783</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.133240356202803</v>
       </c>
       <c r="E6">
-        <v>-13.12759990601721</v>
+        <v>-10.25421522104025</v>
       </c>
       <c r="F6">
-        <v>-1.481219639173957</v>
+        <v>-0.48539445242892</v>
       </c>
       <c r="G6">
-        <v>-8.599969039188494</v>
+        <v>-5.822825141813474</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.376436997418939</v>
       </c>
       <c r="E7">
-        <v>-13.23311335039593</v>
+        <v>-10.53637537951018</v>
       </c>
       <c r="F7">
-        <v>-1.454137823674233</v>
+        <v>-0.2651017387980307</v>
       </c>
       <c r="G7">
-        <v>-8.175247720533971</v>
+        <v>-6.352145241339977</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.449247190001255</v>
       </c>
       <c r="E8">
-        <v>-13.52097938611552</v>
+        <v>-12.32684343266288</v>
       </c>
       <c r="F8">
-        <v>-1.311321484859778</v>
+        <v>-0.150427525758884</v>
       </c>
       <c r="G8">
-        <v>-7.598717405210178</v>
+        <v>-5.752902310381707</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.302765375916497</v>
       </c>
       <c r="E9">
-        <v>-14.78258507380843</v>
+        <v>-10.77073749482914</v>
       </c>
       <c r="F9">
-        <v>-1.279977719072651</v>
+        <v>-0.2726887558402714</v>
       </c>
       <c r="G9">
-        <v>-7.766489544766145</v>
+        <v>-5.371230618587098</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.909681095216557</v>
       </c>
       <c r="E10">
-        <v>-15.21123683795249</v>
+        <v>-12.683506045507</v>
       </c>
       <c r="F10">
-        <v>-1.189978085860693</v>
+        <v>-0.7076354861911939</v>
       </c>
       <c r="G10">
-        <v>-7.44382734149659</v>
+        <v>-5.272620067061105</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.274261240264872</v>
       </c>
       <c r="E11">
-        <v>-15.27175083611698</v>
+        <v>-14.08677598558187</v>
       </c>
       <c r="F11">
-        <v>-1.082416235341983</v>
+        <v>-0.1044928965388458</v>
       </c>
       <c r="G11">
-        <v>-7.1323573849663</v>
+        <v>-4.655310730196534</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.430014028694164</v>
       </c>
       <c r="E12">
-        <v>-16.16763696295044</v>
+        <v>-12.93209209768406</v>
       </c>
       <c r="F12">
-        <v>-1.023682501381289</v>
+        <v>-0.1736035889544086</v>
       </c>
       <c r="G12">
-        <v>-6.966783663855161</v>
+        <v>-4.780472926581552</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.428275634222483</v>
       </c>
       <c r="E13">
-        <v>-16.78498571052011</v>
+        <v>-13.69992656500262</v>
       </c>
       <c r="F13">
-        <v>-0.5530538451547781</v>
+        <v>-0.2525163528472978</v>
       </c>
       <c r="G13">
-        <v>-6.351607121004228</v>
+        <v>-3.582836901048909</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.343613542426185</v>
       </c>
       <c r="E14">
-        <v>-18.68871089860465</v>
+        <v>-15.8008622676472</v>
       </c>
       <c r="F14">
-        <v>-0.9370402412528777</v>
+        <v>0.2273742793099146</v>
       </c>
       <c r="G14">
-        <v>-6.387241187139796</v>
+        <v>-3.725261604058166</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.252075502143778</v>
       </c>
       <c r="E15">
-        <v>-19.18303912128195</v>
+        <v>-16.20915401265276</v>
       </c>
       <c r="F15">
-        <v>-0.6466378241186495</v>
+        <v>0.8464115826871795</v>
       </c>
       <c r="G15">
-        <v>-6.13685445116013</v>
+        <v>-3.649170076094643</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.219217183206533</v>
       </c>
       <c r="E16">
-        <v>-19.60987496734893</v>
+        <v>-17.05474690715704</v>
       </c>
       <c r="F16">
-        <v>-0.3356844400883682</v>
+        <v>0.8226009900611105</v>
       </c>
       <c r="G16">
-        <v>-5.320132155241865</v>
+        <v>-3.537818541253327</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.302660630946577</v>
       </c>
       <c r="E17">
-        <v>-20.85205803002295</v>
+        <v>-17.81817969774014</v>
       </c>
       <c r="F17">
-        <v>-0.02232630548776003</v>
+        <v>1.502389102024886</v>
       </c>
       <c r="G17">
-        <v>-5.348399878976481</v>
+        <v>-1.809648364217187</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.53694145882948</v>
       </c>
       <c r="E18">
-        <v>-20.7970687701478</v>
+        <v>-18.51890218026503</v>
       </c>
       <c r="F18">
-        <v>0.5244119193405669</v>
+        <v>1.540598376846416</v>
       </c>
       <c r="G18">
-        <v>-4.735940187576768</v>
+        <v>-2.260996795826605</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9330262740670129</v>
       </c>
       <c r="E19">
-        <v>-21.14799833489821</v>
+        <v>-18.9786736177898</v>
       </c>
       <c r="F19">
-        <v>0.6043029851361624</v>
+        <v>1.570573679684119</v>
       </c>
       <c r="G19">
-        <v>-4.784748358273508</v>
+        <v>-1.803276231948746</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4903317317084286</v>
       </c>
       <c r="E20">
-        <v>-21.99769855532744</v>
+        <v>-17.87716307169005</v>
       </c>
       <c r="F20">
-        <v>1.01823651958027</v>
+        <v>2.043520107903662</v>
       </c>
       <c r="G20">
-        <v>-4.316698508926517</v>
+        <v>-1.074579266805704</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1892972604774901</v>
       </c>
       <c r="E21">
-        <v>-22.14077569159978</v>
+        <v>-21.17670433163283</v>
       </c>
       <c r="F21">
-        <v>1.131711256620163</v>
+        <v>1.848487629853741</v>
       </c>
       <c r="G21">
-        <v>-3.750024983167295</v>
+        <v>-1.791011025759541</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.001488269721022473</v>
       </c>
       <c r="E22">
-        <v>-23.00620783073166</v>
+        <v>-20.51093713997315</v>
       </c>
       <c r="F22">
-        <v>1.056782111567336</v>
+        <v>2.55186267524483</v>
       </c>
       <c r="G22">
-        <v>-3.869917537727846</v>
+        <v>-2.077300888042652</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.0976350715971334</v>
       </c>
       <c r="E23">
-        <v>-23.34250136748927</v>
+        <v>-21.95517618439541</v>
       </c>
       <c r="F23">
-        <v>1.211373693012586</v>
+        <v>2.244694101877939</v>
       </c>
       <c r="G23">
-        <v>-4.363081856890827</v>
+        <v>-2.278922109205852</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.1346768770024252</v>
       </c>
       <c r="E24">
-        <v>-24.47873172380583</v>
+        <v>-21.54446623426975</v>
       </c>
       <c r="F24">
-        <v>1.448064767749294</v>
+        <v>2.928617423916489</v>
       </c>
       <c r="G24">
-        <v>-3.85163785242018</v>
+        <v>-1.681680723398843</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1317381237551949</v>
       </c>
       <c r="E25">
-        <v>-24.31484172099423</v>
+        <v>-22.2968223774301</v>
       </c>
       <c r="F25">
-        <v>1.694409636198228</v>
+        <v>2.498040331615335</v>
       </c>
       <c r="G25">
-        <v>-4.203896674155926</v>
+        <v>-0.09408135919087433</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.1041923522730695</v>
       </c>
       <c r="E26">
-        <v>-23.78180863097337</v>
+        <v>-23.12867135332109</v>
       </c>
       <c r="F26">
-        <v>1.503058422886348</v>
+        <v>2.710654079422273</v>
       </c>
       <c r="G26">
-        <v>-3.513481720946926</v>
+        <v>-2.198010466771505</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.0651150984960628</v>
       </c>
       <c r="E27">
-        <v>-24.79384558762957</v>
+        <v>-22.31647142614938</v>
       </c>
       <c r="F27">
-        <v>1.516375257253753</v>
+        <v>2.556410412286199</v>
       </c>
       <c r="G27">
-        <v>-4.007253066098404</v>
+        <v>-1.417883634905726</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.02109789873532378</v>
       </c>
       <c r="E28">
-        <v>-24.31206576642753</v>
+        <v>-22.69510619487871</v>
       </c>
       <c r="F28">
-        <v>1.36597852833628</v>
+        <v>2.604374541643096</v>
       </c>
       <c r="G28">
-        <v>-3.895425754130969</v>
+        <v>-2.017303751828206</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.02529434523440437</v>
       </c>
       <c r="E29">
-        <v>-22.79008188024158</v>
+        <v>-20.22148160987687</v>
       </c>
       <c r="F29">
-        <v>1.334235489461003</v>
+        <v>2.629525432726894</v>
       </c>
       <c r="G29">
-        <v>-3.946360156398229</v>
+        <v>-2.123966421061075</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.07231821427991017</v>
       </c>
       <c r="E30">
-        <v>-23.69009797537003</v>
+        <v>-22.10362861931486</v>
       </c>
       <c r="F30">
-        <v>1.604813417911433</v>
+        <v>2.789171712064026</v>
       </c>
       <c r="G30">
-        <v>-3.602461887195948</v>
+        <v>-0.7478089741437234</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1198742797485991</v>
       </c>
       <c r="E31">
-        <v>-22.84847202409648</v>
+        <v>-21.68944532962531</v>
       </c>
       <c r="F31">
-        <v>1.372267493658334</v>
+        <v>2.314315068613626</v>
       </c>
       <c r="G31">
-        <v>-3.403852827424318</v>
+        <v>-1.002389111276361</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.166023638012106</v>
       </c>
       <c r="E32">
-        <v>-22.7092712615747</v>
+        <v>-21.26981428570454</v>
       </c>
       <c r="F32">
-        <v>1.243522631915235</v>
+        <v>2.256019541009014</v>
       </c>
       <c r="G32">
-        <v>-3.483507762001398</v>
+        <v>-3.066041224214807</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2076181096650697</v>
       </c>
       <c r="E33">
-        <v>-22.34881378751216</v>
+        <v>-20.24723051308449</v>
       </c>
       <c r="F33">
-        <v>0.7916034818483531</v>
+        <v>2.172013145956311</v>
       </c>
       <c r="G33">
-        <v>-3.366571588065908</v>
+        <v>-0.6478596842214779</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.2404394209020004</v>
       </c>
       <c r="E34">
-        <v>-22.30868245085618</v>
+        <v>-19.79881195989695</v>
       </c>
       <c r="F34">
-        <v>0.7839940988862367</v>
+        <v>2.738649584167284</v>
       </c>
       <c r="G34">
-        <v>-3.480298727316261</v>
+        <v>-2.115271183928547</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2593767870954565</v>
       </c>
       <c r="E35">
-        <v>-21.75230507732579</v>
+        <v>-20.41359306270427</v>
       </c>
       <c r="F35">
-        <v>0.9984401953881672</v>
+        <v>2.724469590966163</v>
       </c>
       <c r="G35">
-        <v>-4.056333578184579</v>
+        <v>-2.410630342601963</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2593338069056251</v>
       </c>
       <c r="E36">
-        <v>-21.31450126721223</v>
+        <v>-17.50162577918196</v>
       </c>
       <c r="F36">
-        <v>1.328930624613475</v>
+        <v>2.737937188200877</v>
       </c>
       <c r="G36">
-        <v>-3.656641417585499</v>
+        <v>-1.304323837954904</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2370369714524428</v>
       </c>
       <c r="E37">
-        <v>-21.25965239003133</v>
+        <v>-19.21739212510414</v>
       </c>
       <c r="F37">
-        <v>1.151128188541783</v>
+        <v>2.806055496467886</v>
       </c>
       <c r="G37">
-        <v>-3.715184972649111</v>
+        <v>-2.20950130467268</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.192655848844195</v>
       </c>
       <c r="E38">
-        <v>-21.1759209056295</v>
+        <v>-19.39455508523222</v>
       </c>
       <c r="F38">
-        <v>1.068863021769764</v>
+        <v>2.064592117896077</v>
       </c>
       <c r="G38">
-        <v>-3.792323210290097</v>
+        <v>-1.01172746783454</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.1297771322854603</v>
       </c>
       <c r="E39">
-        <v>-20.37737885606493</v>
+        <v>-18.64949431369823</v>
       </c>
       <c r="F39">
-        <v>1.135626120965793</v>
+        <v>2.911229992131728</v>
       </c>
       <c r="G39">
-        <v>-3.640720930579073</v>
+        <v>-1.493788133240361</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.05431700632877471</v>
       </c>
       <c r="E40">
-        <v>-19.44906432686254</v>
+        <v>-18.56683154916221</v>
       </c>
       <c r="F40">
-        <v>1.095006297002117</v>
+        <v>2.479627380985907</v>
       </c>
       <c r="G40">
-        <v>-3.634919730861975</v>
+        <v>-1.273355668876865</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.02601825215927483</v>
       </c>
       <c r="E41">
-        <v>-18.84948078282497</v>
+        <v>-15.78736741510434</v>
       </c>
       <c r="F41">
-        <v>1.019174231480239</v>
+        <v>2.639474125234516</v>
       </c>
       <c r="G41">
-        <v>-3.363769424854142</v>
+        <v>-1.159428375111385</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1027488810589081</v>
       </c>
       <c r="E42">
-        <v>-19.03386665899528</v>
+        <v>-16.93327964884929</v>
       </c>
       <c r="F42">
-        <v>0.8472432635595902</v>
+        <v>1.92989460799646</v>
       </c>
       <c r="G42">
-        <v>-4.062036341254894</v>
+        <v>-1.866525058728602</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.169468420347425</v>
       </c>
       <c r="E43">
-        <v>-18.59818670319132</v>
+        <v>-15.97546663996094</v>
       </c>
       <c r="F43">
-        <v>1.351130871008501</v>
+        <v>2.285320552780838</v>
       </c>
       <c r="G43">
-        <v>-4.042772289479394</v>
+        <v>-2.274705739501965</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2219186214459964</v>
       </c>
       <c r="E44">
-        <v>-18.75716784017861</v>
+        <v>-15.86408882174229</v>
       </c>
       <c r="F44">
-        <v>0.9082972546155249</v>
+        <v>1.795844881405833</v>
       </c>
       <c r="G44">
-        <v>-3.864031026250202</v>
+        <v>-1.274582845740097</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.2585581078141668</v>
       </c>
       <c r="E45">
-        <v>-17.10040298210237</v>
+        <v>-15.63878818291268</v>
       </c>
       <c r="F45">
-        <v>1.139502880410895</v>
+        <v>1.997343595402007</v>
       </c>
       <c r="G45">
-        <v>-4.235852490923358</v>
+        <v>-1.23384976130115</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.2816719098091323</v>
       </c>
       <c r="E46">
-        <v>-17.16885086672831</v>
+        <v>-14.48174948853088</v>
       </c>
       <c r="F46">
-        <v>1.286816425855148</v>
+        <v>1.874418843030977</v>
       </c>
       <c r="G46">
-        <v>-4.457220103431296</v>
+        <v>-0.7092316522693318</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.297319542364095</v>
       </c>
       <c r="E47">
-        <v>-16.48473429838954</v>
+        <v>-15.57995877707903</v>
       </c>
       <c r="F47">
-        <v>1.061868287420525</v>
+        <v>2.231148638107362</v>
       </c>
       <c r="G47">
-        <v>-3.820102032012356</v>
+        <v>-1.062894836832521</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.3122983583583352</v>
       </c>
       <c r="E48">
-        <v>-16.74856772255043</v>
+        <v>-13.47808568031486</v>
       </c>
       <c r="F48">
-        <v>0.941552892368314</v>
+        <v>2.25705997046693</v>
       </c>
       <c r="G48">
-        <v>-3.995713009873838</v>
+        <v>-1.417138797611732</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.333359727363611</v>
       </c>
       <c r="E49">
-        <v>-15.58414308706212</v>
+        <v>-14.22906969585089</v>
       </c>
       <c r="F49">
-        <v>0.8171917509208297</v>
+        <v>1.580729464042441</v>
       </c>
       <c r="G49">
-        <v>-4.006324480397081</v>
+        <v>-1.505403657560795</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.3659075269966423</v>
       </c>
       <c r="E50">
-        <v>-15.14711817447788</v>
+        <v>-13.24980077711419</v>
       </c>
       <c r="F50">
-        <v>0.8460321904166973</v>
+        <v>1.670491355809795</v>
       </c>
       <c r="G50">
-        <v>-4.360850626230405</v>
+        <v>-2.298619282227198</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.4134719044457851</v>
       </c>
       <c r="E51">
-        <v>-14.72474287530846</v>
+        <v>-11.74669609906623</v>
       </c>
       <c r="F51">
-        <v>0.8812245511572315</v>
+        <v>1.508368257938292</v>
       </c>
       <c r="G51">
-        <v>-4.344943264110217</v>
+        <v>-1.752633858400276</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.4763288469707335</v>
       </c>
       <c r="E52">
-        <v>-14.05043045319631</v>
+        <v>-11.59585715834473</v>
       </c>
       <c r="F52">
-        <v>0.9379213296744409</v>
+        <v>1.374611773408256</v>
       </c>
       <c r="G52">
-        <v>-4.637565884003056</v>
+        <v>-1.699464944251034</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.5506996156976843</v>
       </c>
       <c r="E53">
-        <v>-12.94645641723639</v>
+        <v>-12.13742189339604</v>
       </c>
       <c r="F53">
-        <v>0.7264407884745326</v>
+        <v>2.012872170734886</v>
       </c>
       <c r="G53">
-        <v>-4.819762273534343</v>
+        <v>-1.581642840494493</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.6314506191640181</v>
       </c>
       <c r="E54">
-        <v>-13.17099627243271</v>
+        <v>-11.00014998805772</v>
       </c>
       <c r="F54">
-        <v>0.6583945481715673</v>
+        <v>0.9664387058832167</v>
       </c>
       <c r="G54">
-        <v>-4.105679869217068</v>
+        <v>-1.637436731891291</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7131029901667936</v>
       </c>
       <c r="E55">
-        <v>-12.22597620261603</v>
+        <v>-11.1007364527161</v>
       </c>
       <c r="F55">
-        <v>1.014858437311653</v>
+        <v>1.697376848235056</v>
       </c>
       <c r="G55">
-        <v>-4.762304802806907</v>
+        <v>-1.810996946278119</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.7900362047221559</v>
       </c>
       <c r="E56">
-        <v>-12.30947220636946</v>
+        <v>-10.14048712481162</v>
       </c>
       <c r="F56">
-        <v>0.6392302683078007</v>
+        <v>1.606950605810656</v>
       </c>
       <c r="G56">
-        <v>-5.224756888173485</v>
+        <v>-3.460339056570159</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.8566399623528445</v>
       </c>
       <c r="E57">
-        <v>-11.45008105156382</v>
+        <v>-10.3786984430371</v>
       </c>
       <c r="F57">
-        <v>0.6623624280309769</v>
+        <v>1.774262597093295</v>
       </c>
       <c r="G57">
-        <v>-5.303588236139144</v>
+        <v>-1.45443644307794</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.9079469574680117</v>
       </c>
       <c r="E58">
-        <v>-12.34463580703902</v>
+        <v>-8.610347456937859</v>
       </c>
       <c r="F58">
-        <v>0.5900492672361913</v>
+        <v>1.14060792252623</v>
       </c>
       <c r="G58">
-        <v>-5.835467688482014</v>
+        <v>-2.433352801901117</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.939836972096263</v>
       </c>
       <c r="E59">
-        <v>-11.64995430884036</v>
+        <v>-8.891977783948885</v>
       </c>
       <c r="F59">
-        <v>0.7669131630405109</v>
+        <v>1.546575876025017</v>
       </c>
       <c r="G59">
-        <v>-5.252663677536563</v>
+        <v>-2.521748910712558</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.9516339531953707</v>
       </c>
       <c r="E60">
-        <v>-11.16699255592232</v>
+        <v>-8.627994920145749</v>
       </c>
       <c r="F60">
-        <v>0.2570066380428584</v>
+        <v>1.27104265377104</v>
       </c>
       <c r="G60">
-        <v>-5.349289090019091</v>
+        <v>-2.211995033057858</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.9459740504365807</v>
       </c>
       <c r="E61">
-        <v>-10.6688151303385</v>
+        <v>-8.381836130036804</v>
       </c>
       <c r="F61">
-        <v>0.5385960543787028</v>
+        <v>0.7914378083677931</v>
       </c>
       <c r="G61">
-        <v>-5.712375942901005</v>
+        <v>-2.196606103944062</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.9271008714271974</v>
       </c>
       <c r="E62">
-        <v>-10.48649423831569</v>
+        <v>-8.196956650199654</v>
       </c>
       <c r="F62">
-        <v>0.2022946278227567</v>
+        <v>1.826792687574422</v>
       </c>
       <c r="G62">
-        <v>-5.154325467400004</v>
+        <v>-2.925893688967804</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.8994947613083901</v>
       </c>
       <c r="E63">
-        <v>-9.809958335465767</v>
+        <v>-8.372118024816345</v>
       </c>
       <c r="F63">
-        <v>0.4343567855126214</v>
+        <v>1.165261793168348</v>
       </c>
       <c r="G63">
-        <v>-5.769718570873861</v>
+        <v>-2.634298091423071</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.8673238664581121</v>
       </c>
       <c r="E64">
-        <v>-9.96071576365512</v>
+        <v>-8.902837064619279</v>
       </c>
       <c r="F64">
-        <v>0.05953213288948432</v>
+        <v>0.9385045003260117</v>
       </c>
       <c r="G64">
-        <v>-6.233414239211469</v>
+        <v>-3.153364373576309</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.8342088897588035</v>
       </c>
       <c r="E65">
-        <v>-9.818711875722594</v>
+        <v>-8.001539411346656</v>
       </c>
       <c r="F65">
-        <v>0.2353746516861522</v>
+        <v>0.4163248838884818</v>
       </c>
       <c r="G65">
-        <v>-5.607790286915264</v>
+        <v>-3.83538596203625</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.8042222362570021</v>
       </c>
       <c r="E66">
-        <v>-9.823806408981223</v>
+        <v>-6.683662905634428</v>
       </c>
       <c r="F66">
-        <v>-0.1657647482217168</v>
+        <v>0.571474784963218</v>
       </c>
       <c r="G66">
-        <v>-5.880610734696854</v>
+        <v>-3.268492594432546</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7785621700238868</v>
       </c>
       <c r="E67">
-        <v>-8.864888452435002</v>
+        <v>-6.615020296626161</v>
       </c>
       <c r="F67">
-        <v>-0.08466426601803402</v>
+        <v>0.7549233732523909</v>
       </c>
       <c r="G67">
-        <v>-5.214995254034137</v>
+        <v>-3.061575481672402</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.7554183828391872</v>
       </c>
       <c r="E68">
-        <v>-9.736243835568908</v>
+        <v>-8.222719138829291</v>
       </c>
       <c r="F68">
-        <v>-0.0774881192075819</v>
+        <v>0.8634660107760157</v>
       </c>
       <c r="G68">
-        <v>-6.378224390294442</v>
+        <v>-3.789439016539345</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.7328859988618057</v>
       </c>
       <c r="E69">
-        <v>-9.498227241725754</v>
+        <v>-6.909122041054312</v>
       </c>
       <c r="F69">
-        <v>-0.06867926024621196</v>
+        <v>0.435287870473368</v>
       </c>
       <c r="G69">
-        <v>-6.222861830676295</v>
+        <v>-3.517169813979742</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.7082286949704631</v>
       </c>
       <c r="E70">
-        <v>-9.613902581777687</v>
+        <v>-7.74686709010329</v>
       </c>
       <c r="F70">
-        <v>-0.2558256806214819</v>
+        <v>0.1687681139292523</v>
       </c>
       <c r="G70">
-        <v>-5.5415161738576</v>
+        <v>-3.271704910339242</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.6796512556736396</v>
       </c>
       <c r="E71">
-        <v>-9.463738383683337</v>
+        <v>-7.363907628696631</v>
       </c>
       <c r="F71">
-        <v>-0.5384232200865332</v>
+        <v>0.5529061012620643</v>
       </c>
       <c r="G71">
-        <v>-5.732519362054436</v>
+        <v>-3.630152115936102</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.6479601533526975</v>
       </c>
       <c r="E72">
-        <v>-10.11139167931234</v>
+        <v>-7.505540181760529</v>
       </c>
       <c r="F72">
-        <v>-0.2691102086601775</v>
+        <v>-0.2703179683334592</v>
       </c>
       <c r="G72">
-        <v>-5.159227612409815</v>
+        <v>-4.027573671216046</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.6141286531395654</v>
       </c>
       <c r="E73">
-        <v>-9.755498907049523</v>
+        <v>-7.440706019392713</v>
       </c>
       <c r="F73">
-        <v>-0.885633416969946</v>
+        <v>-0.05205061300241469</v>
       </c>
       <c r="G73">
-        <v>-5.134867823552497</v>
+        <v>-3.735056050413109</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.578431744305547</v>
       </c>
       <c r="E74">
-        <v>-10.62652371158087</v>
+        <v>-8.14255609194551</v>
       </c>
       <c r="F74">
-        <v>-1.024046154671118</v>
+        <v>-0.02741662317796299</v>
       </c>
       <c r="G74">
-        <v>-5.063671878155666</v>
+        <v>-2.488684041058034</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.5418237953359227</v>
       </c>
       <c r="E75">
-        <v>-10.61820943330279</v>
+        <v>-7.543588420372975</v>
       </c>
       <c r="F75">
-        <v>-0.9192634767888003</v>
+        <v>0.1514602054151594</v>
       </c>
       <c r="G75">
-        <v>-4.767416945996521</v>
+        <v>-2.628877513406868</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.505027201738542</v>
       </c>
       <c r="E76">
-        <v>-11.01770235331145</v>
+        <v>-8.906074923534764</v>
       </c>
       <c r="F76">
-        <v>-0.6961112388834471</v>
+        <v>-0.1912917181063864</v>
       </c>
       <c r="G76">
-        <v>-4.596343897551752</v>
+        <v>-2.339230961468445</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.4676243799184892</v>
       </c>
       <c r="E77">
-        <v>-10.4091026175246</v>
+        <v>-8.903095187637717</v>
       </c>
       <c r="F77">
-        <v>-1.086819008087862</v>
+        <v>-0.4890492094100715</v>
       </c>
       <c r="G77">
-        <v>-5.117352662868181</v>
+        <v>-2.762016359402897</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.4264039983143853</v>
       </c>
       <c r="E78">
-        <v>-11.34672316081275</v>
+        <v>-9.108936973656373</v>
       </c>
       <c r="F78">
-        <v>-0.824282870383809</v>
+        <v>-0.2449823513188363</v>
       </c>
       <c r="G78">
-        <v>-4.247172705303443</v>
+        <v>-2.866749670358813</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.3746800091719218</v>
       </c>
       <c r="E79">
-        <v>-11.89052949049785</v>
+        <v>-11.5017871677834</v>
       </c>
       <c r="F79">
-        <v>-0.9968268301825293</v>
+        <v>0.04140911085103673</v>
       </c>
       <c r="G79">
-        <v>-4.096485886407503</v>
+        <v>-4.189098364922831</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.3041979561563234</v>
       </c>
       <c r="E80">
-        <v>-11.94982985762829</v>
+        <v>-9.693739578532915</v>
       </c>
       <c r="F80">
-        <v>-1.178904470420069</v>
+        <v>-0.3916862183546288</v>
       </c>
       <c r="G80">
-        <v>-4.140391912094433</v>
+        <v>-2.184462302952557</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.2071692623926781</v>
       </c>
       <c r="E81">
-        <v>-12.39765970919483</v>
+        <v>-10.17440086665506</v>
       </c>
       <c r="F81">
-        <v>-0.9425348022356468</v>
+        <v>-0.9196884292664365</v>
       </c>
       <c r="G81">
-        <v>-3.404046419496326</v>
+        <v>-2.302615810086602</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.07909676767478921</v>
       </c>
       <c r="E82">
-        <v>-14.27842553406049</v>
+        <v>-12.00518139542405</v>
       </c>
       <c r="F82">
-        <v>-1.189953234838609</v>
+        <v>-0.9039328812651899</v>
       </c>
       <c r="G82">
-        <v>-3.737149469768034</v>
+        <v>-2.636444010322948</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.08303514666130003</v>
       </c>
       <c r="E83">
-        <v>-13.89477321613065</v>
+        <v>-12.37848615024635</v>
       </c>
       <c r="F83">
-        <v>-1.371686274236584</v>
+        <v>-0.888302416741766</v>
       </c>
       <c r="G83">
-        <v>-2.995964175369746</v>
+        <v>-3.086253549020986</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.2816783584455725</v>
       </c>
       <c r="E84">
-        <v>-15.60711603570303</v>
+        <v>-13.92114704875132</v>
       </c>
       <c r="F84">
-        <v>-1.623036138533232</v>
+        <v>-0.3971584134175223</v>
       </c>
       <c r="G84">
-        <v>-4.120648801971255</v>
+        <v>-1.567881397274182</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.5165720255092219</v>
       </c>
       <c r="E85">
-        <v>-15.95368920845806</v>
+        <v>-14.99482559359993</v>
       </c>
       <c r="F85">
-        <v>-1.492477980545405</v>
+        <v>-0.7684625045787615</v>
       </c>
       <c r="G85">
-        <v>-2.889173538496058</v>
+        <v>-1.789419633303211</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7840882416864139</v>
       </c>
       <c r="E86">
-        <v>-17.47048799190522</v>
+        <v>-15.44931230195774</v>
       </c>
       <c r="F86">
-        <v>-1.823301413466638</v>
+        <v>-0.9664928442594142</v>
       </c>
       <c r="G86">
-        <v>-2.738142191336377</v>
+        <v>-0.9865309674795643</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.074807721877059</v>
       </c>
       <c r="E87">
-        <v>-18.54392199915741</v>
+        <v>-17.20653682742014</v>
       </c>
       <c r="F87">
-        <v>-1.878309150849539</v>
+        <v>-0.7227623033337156</v>
       </c>
       <c r="G87">
-        <v>-2.989539543556353</v>
+        <v>-2.447724552331485</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.374669578352984</v>
       </c>
       <c r="E88">
-        <v>-19.8408180847921</v>
+        <v>-17.9313326777698</v>
       </c>
       <c r="F88">
-        <v>-1.911413197367616</v>
+        <v>-0.9896813329659807</v>
       </c>
       <c r="G88">
-        <v>-2.639321641630581</v>
+        <v>-1.299844970526262</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.672402989409686</v>
       </c>
       <c r="E89">
-        <v>-21.58715615874006</v>
+        <v>-20.70226969527123</v>
       </c>
       <c r="F89">
-        <v>-2.151756543983267</v>
+        <v>-1.132319572788833</v>
       </c>
       <c r="G89">
-        <v>-2.488539667309418</v>
+        <v>-1.459686397573052</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.95868840101095</v>
       </c>
       <c r="E90">
-        <v>-22.60160226356833</v>
+        <v>-23.81956704724933</v>
       </c>
       <c r="F90">
-        <v>-2.221160478459421</v>
+        <v>-0.6109086813011011</v>
       </c>
       <c r="G90">
-        <v>-2.776758887869482</v>
+        <v>-1.720553355213585</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.22663444249975</v>
       </c>
       <c r="E91">
-        <v>-24.44024422321464</v>
+        <v>-22.47474159271746</v>
       </c>
       <c r="F91">
-        <v>-2.144765123103639</v>
+        <v>-1.571334415454904</v>
       </c>
       <c r="G91">
-        <v>-2.175222383041161</v>
+        <v>-0.234767014773626</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.476510616613863</v>
       </c>
       <c r="E92">
-        <v>-26.59145504429237</v>
+        <v>-25.69535155070654</v>
       </c>
       <c r="F92">
-        <v>-2.634713792265643</v>
+        <v>-1.280777921983755</v>
       </c>
       <c r="G92">
-        <v>-2.579150600673484</v>
+        <v>-1.524821926749589</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.708554337964345</v>
       </c>
       <c r="E93">
-        <v>-28.40481906202786</v>
+        <v>-26.9087425756398</v>
       </c>
       <c r="F93">
-        <v>-2.711411501723447</v>
+        <v>-1.811623089821971</v>
       </c>
       <c r="G93">
-        <v>-2.568896783300219</v>
+        <v>-2.088502978446596</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.922446222957106</v>
       </c>
       <c r="E94">
-        <v>-30.26094772405478</v>
+        <v>-29.23352074848352</v>
       </c>
       <c r="F94">
-        <v>-2.743840428808242</v>
+        <v>-1.651262757783625</v>
       </c>
       <c r="G94">
-        <v>-3.019218192561531</v>
+        <v>-1.008853117748467</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.12349053915949</v>
       </c>
       <c r="E95">
-        <v>-32.36630095309384</v>
+        <v>-32.18656129125539</v>
       </c>
       <c r="F95">
-        <v>-2.474413931047703</v>
+        <v>-1.680688853033272</v>
       </c>
       <c r="G95">
-        <v>-2.601718842559344</v>
+        <v>-2.381525907369688</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.316235111776354</v>
       </c>
       <c r="E96">
-        <v>-34.45749137967391</v>
+        <v>-33.3373416345586</v>
       </c>
       <c r="F96">
-        <v>-2.690354402344283</v>
+        <v>-1.896175378993119</v>
       </c>
       <c r="G96">
-        <v>-2.48551438103161</v>
+        <v>-1.984609660209898</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.500462272726891</v>
       </c>
       <c r="E97">
-        <v>-37.09252889220515</v>
+        <v>-37.10407876516172</v>
       </c>
       <c r="F97">
-        <v>-2.814862993189466</v>
+        <v>-2.230540910928723</v>
       </c>
       <c r="G97">
-        <v>-2.999668674510359</v>
+        <v>-1.650512399805678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.682993667909706</v>
       </c>
       <c r="E98">
-        <v>-39.61768751141428</v>
+        <v>-37.08928650481566</v>
       </c>
       <c r="F98">
-        <v>-3.175399964849117</v>
+        <v>-2.447150703086765</v>
       </c>
       <c r="G98">
-        <v>-3.578039755129001</v>
+        <v>-0.5406884256468946</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.857339341635411</v>
       </c>
       <c r="E99">
-        <v>-41.72960023505345</v>
+        <v>-42.84487281366251</v>
       </c>
       <c r="F99">
-        <v>-3.438121656851397</v>
+        <v>-2.651295222567481</v>
       </c>
       <c r="G99">
-        <v>-3.224852347691931</v>
+        <v>-2.047628801480593</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.028649332779948</v>
       </c>
       <c r="E100">
-        <v>-44.89633493777329</v>
+        <v>-43.71176312142485</v>
       </c>
       <c r="F100">
-        <v>-3.51983181746354</v>
+        <v>-2.092298816912527</v>
       </c>
       <c r="G100">
-        <v>-3.396794919849953</v>
+        <v>-1.795017397283623</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.182606666682889</v>
       </c>
       <c r="E101">
-        <v>-46.8378253348448</v>
+        <v>-45.14697238867582</v>
       </c>
       <c r="F101">
-        <v>-3.694281022288699</v>
+        <v>-2.890710797691997</v>
       </c>
       <c r="G101">
-        <v>-3.529730330109296</v>
+        <v>-2.485543912025645</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.329089253320871</v>
       </c>
       <c r="E102">
-        <v>-50.11200827246313</v>
+        <v>-48.19858648940966</v>
       </c>
       <c r="F102">
-        <v>-3.809454740871734</v>
+        <v>-2.708747472156043</v>
       </c>
       <c r="G102">
-        <v>-4.03747311666089</v>
+        <v>-1.593583205749312</v>
       </c>
     </row>
   </sheetData>
